--- a/noticias_registro.xlsx
+++ b/noticias_registro.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,6 +526,94 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Nathalie Cook: “Debemos crear equilibrio entre el uso de la tecnología y la defensa de nuestra ancestralidad” - adn.celam.org</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Nathalie Cook: “Debemos crear equilibrio entre el uso de la tecnología y la defensa de nuestra ancestralidad”  adn.celam.org</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNdUZaWmUzUTdTVFRlN0NMaUtOQy03NGpZS1RWemV1Q1QtNURxZUJNd0JNMER5OWg0eDhndFFZbTBNcm94ZGxRTnpaTkZVN21CSkMyQ1pzMDRyZ2l1UHFGUkRXT0h2WVZzZnRpYUdNMGdrNlRBSTBmcENyTWN5YzI3WUhHSF9hM0NBb2ZWWUh5VERROGRVajNmTU5uUW5yaGQ1ZVBVVnJBMDcwN2I1YzVaRkpXMjBTWXRLZVgzc2dfcUdKd3pHQVdqVlRpWmJIODFWa1ZhWkl5eW5NcHFJTVJ3WmQzSQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tecnología permite reforzar la seguridad y respuesta en el Quindío - Crónica del Quindio</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tecnología permite reforzar la seguridad y respuesta en el Quindío  Crónica del Quindio</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQdjFqUE1nM0xhNFNiT240NlZLVHNrT3lKY3BKbEtKZlRsSjJtQXRsWVBPelMwT0VPTzI3WlZLZVJVR051SVViUFBiQzljZ2RLZWREeERZZDhNckY2WklnR0FGRzBZNXo5RVJtT3otNWk2bEpGb2QxdHlKb0E0NDJ3X2VseGJLS2k0M0haOXhiZTFRcUJrVDBkN0taYS1MV1BYQmZ6RlQ2WXY?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>¡Triunfo de Atlético Nacional en la Serie Colombia! - ESPN Argentina</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>¡Triunfo de Atlético Nacional en la Serie Colombia!  ESPN Argentina</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOM0RvU2FDRnNvaks3YlJwUXZWT28yaTdHeDRlaXlROThIdDJfZGNHeU4xREZxWHF0WlhoakVaajNsMmVVQ3NBLWE0LWkxRWpvZXlFUVFDMEVoOWpJYkpiTThXR011alFPUjR0eF9ZdDBqNVJXLWsxR3oydXBPZmVjS2pFVEgtT1ZGejFLRWMxUjhCMklqaDNONU5RNENHYVE?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>La Selección Colombia Femenina Sub-20 visita el Estadio Miejski LKS Łódź - Federación Colombiana de Futbol</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>La Selección Colombia Femenina Sub-20 visita el Estadio Miejski LKS Łódź  Federación Colombiana de Futbol</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPZUtFUVUwQmxydXNRQzJ0RU5xZURZcC13RGNYVVZNbVI1OXlmdGJ3OEpVX280RGFfV2NpU3pHd3BEXzFjMFRDbVAtS0VXbkhtNlV4TlNCTzZvTGNUbktRVUlKZkJzVk1XclBnYnM3Tk8xVnZaaVRIbkpMREZwamZmdUNvNklaX25LQnkxN0FDZ05Rd0dUZ3hSMklXYzdKaWEtNU5iNkNR?oc=5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/noticias_registro.xlsx
+++ b/noticias_registro.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,6 +614,94 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Una conversación con Lila Tretikov - Capgemini</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Una conversación con Lila Tretikov  Capgemini</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOMnNJdDZkYXlwcjVtS1JGT3B2amJNOWpPcW1OYTRRS0gwcVduWXV6ejVPTFJKZGhhYkZ2aVdPaFNzNjVMY3ZMYzIxTjVmMHplZ3hsQ0dSbW9WSmRVVnNGR0lFN0J1NVkyamkySlhfNkN4aUZCU25WSFJDSlp4YTQ2TGViNGw4SEZTTXVjazM3c0J1SGNhZmVSYTIyck0tU3ZwVGxld0pjYw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kia K4 se transforma: estrena tecnología híbrida y apunta a los grandes del segmento - El Carro Colombiano</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Kia K4 se transforma: estrena tecnología híbrida y apunta a los grandes del segmento  El Carro Colombiano</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQRW9tU05xeGdXQlZPWlYzU25XNWE5UVVPSk9uUkZfZkhNUVQ5c0I5WU5CUWg1dE1kTjgyU1Z2S0k4c29PTnY3UnJTMTlRSXpjNlNuNDRhRDh6OGZnVFNhVlF1dmFPb29RTldvTlBxc2ljTlRJaGsyb2x1U1lTSTlhMG1aekZUNEpRZmN3UzJVd29TMGs5UkNabmVYNHBJcWlfa3IxeVhTRjdUcGxQVDhQZg?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tabla del descenso en Colombia: así quedó tras triunfo de Boyacá Chicó y empate de Cúcuta - Caracol Radio</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Tabla del descenso en Colombia: así quedó tras triunfo de Boyacá Chicó y empate de Cúcuta  Caracol Radio</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQblp3WG5XVkZPNFVPMjV4SFBDQW9iX0RiUFB2ckNZQWk4RmNQQUowellrMWFMc19aR0JHeFRCeWEyRlpha1VFZEpJamdmQjducWNPazVoLTh4MVF6OVpKUkc3VWx3N3R5ZnZ3N0p1ZHJ4dVpKLXRXZy1hRGgybWJ3Nnp0d3kyZzdTeHRkZlBlYXlRM0Z5Qklpb1pVRDBQWlJFRF9BTzJUVi1Sa1lQTjh0eFFBck9UTFp1Nzh5X2JmV1PSAdQBQVVfeXFMT2xsUjRLNUZoM3BVZHBzYlRIdXFsSHFaQ1RBYlFDendUa2pLcW5tWmlGWHFmOFhLVFBsOUNWMXlmNGgtOE5ZTnYxQmp0VGUzSzlyMHhuZ0E1U25FZXNra0FXT25MMmtSWnRlMEkySFlBQVFFdG1vZVdDalRnR1U1TVgweEM1cTlFWWJDZ1hFbEtrb05wbUlxY1B5RTFZQ2wtV1k2WmQwQWh1MWRvcHQyNzVveEZNNjYzZDVPeC05UG85a19vbDRObEZWUWR2NjhIYk1tYkg?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Un ataque con drones del ELN deja al menos tres muertos en un cuartel militar en Colombia - EL PAÍS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Un ataque con drones del ELN deja al menos tres muertos en un cuartel militar en Colombia  EL PAÍS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNUW5ISW9WMVk4d2V0UzB2aVFKR1VqNnVCZHVDaF9weV8xVjMzRmwwcS1MVEFGLUtmQTcyNlF5OE1JNERhQ3JoSTl5emNtbHpVeERSWDlYNFZkTzg2aGQ4OHJIWmUxZEd2ODVDZUdMZjRELXc1b0xrYVNBY3RkajlCaVFHY0hOb2NHZm8zM2NZdmFVZW01WmJlMHBPZWJTVE9tbW1mekhFT210WXk4NE1kVDNoSmw4dUg2OWkwS005dTkzRG9ybWZzeTItSXFjcmdlXzM4bHhBcEfSAewBQVVfeXFMUGZqTjdWdnlLb2U5anZPYjQyd3hnV0NPQ0FQNG5hLUJOSVFpeDRCMmxQR00wbWt1V0ZUMUhNcTI0R1pEQ01ucm1vUmVmTzUxUFJ6WmpJU2x5OGczYlJkeTZ5T2d3RFYzenZ6RFM0dnZEbFU1RUs1S29MdDB2RzhpeG1qVkkzRHJ3ZXN4eTJoR193S1padWJ5SEdBaEVMbkhaZUJrSUdLbnVmN2dOcGY1d3dQUUE2VGszcXZCMXgtaThCanpibkdud0xzOUVUdU5qb2NVRlV6eFI1QzM1SXJMMUhOYTg0YjVqWHRpOGc?oc=5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
